--- a/measurement/lahore_recording_manifest.xlsx
+++ b/measurement/lahore_recording_manifest.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lahore 20" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,7 +53,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -57,6 +61,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -470,6 +476,46 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Transcript (no keyterms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Exact Match (no keyterms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>WER (no keyterms)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Notes (no keyterms)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Transcript (with keyterms)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Exact Match (with keyterms)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>WER (with keyterms)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Notes (with keyterms)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -479,7 +525,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>lhr-01.wav</t>
+          <t>lhr-01.mp3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -491,6 +537,42 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24A, Block H, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>S=1, D=1, I=0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24A, Block H, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>S=1, D=1, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -500,7 +582,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>lhr-02.wav</t>
+          <t>lhr-02.mp3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -512,6 +594,42 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>House 17, Street 6, Phase 5, DH, Lahore.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>House 17, Street 6, Phase 5, DHA Lahore.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -521,7 +639,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>lhr-03.wav</t>
+          <t>lhr-03.mp3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -533,6 +651,42 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Flat 8, Block C, Gulberg 3, Lahore.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Flat 8, Block C, Gulberg III, Lahore.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -542,7 +696,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>lhr-04.wav</t>
+          <t>lhr-04.mp3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -554,6 +708,42 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>House 42, Street 11, Model Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>House 42, Street 11, Model Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -563,7 +753,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>lhr-05.wav</t>
+          <t>lhr-05.mp3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -575,6 +765,42 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>अपार्टमेंट टwelve ब्लॉक ई वॉप डे टाउन लाहौर</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>S=7, D=0, I=10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Apartment 12, Block E, Wapda Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -584,7 +810,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>lhr-06.wav</t>
+          <t>lhr-06.mp3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -596,6 +822,42 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>House 9, Street 4, Valencia Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>House 9, Street 4, Valencia Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -605,7 +867,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>lhr-07.wav</t>
+          <t>lhr-07.mp3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -617,6 +879,42 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Shop 14, Liberty Market, Gulberg, Lahore.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Shop 14, Liberty Market, Gulberg, Lahore.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -626,7 +924,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>lhr-08.wav</t>
+          <t>lhr-08.mp3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -638,6 +936,42 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Office 5, M.M. Alam Road, Gulberg 3, Lahore.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>S=2, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Office 5, MM Alam Road, Gulberg III, Lahore.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -647,7 +981,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>lhr-09.wav</t>
+          <t>lhr-09.mp3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -659,6 +993,42 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>House 31, Street 8, Garden Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>House 31, Street 8, Garden Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -668,7 +1038,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>lhr-10.wav</t>
+          <t>lhr-10.mp3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -680,6 +1050,42 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Flat 3, Block B, Faisal Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Flat 3, Block B, Faisal Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -689,7 +1095,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>lhr-11.wav</t>
+          <t>lhr-11.mp3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -701,6 +1107,42 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>House 18, Street 2, Phase 6, DHA, Lahore.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>House 18, Street 2, Phase 6, DHA Lahore.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -710,7 +1152,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>lhr-12.wav</t>
+          <t>lhr-12.mp3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -722,6 +1164,42 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>एपार्टमेंट सेवन ब्लॉक एफ बाहरी टाउन लाहौर।</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>S=7, D=0, I=10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Apartment 7, Block F, Bahria Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -731,7 +1209,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>lhr-13.wav</t>
+          <t>lhr-13.mp3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -743,6 +1221,42 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>House 55, Street 9, Askari 10, Lahore.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>House 55, Street 9, Askari 10, Lahore.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -752,7 +1266,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>lhr-14.wav</t>
+          <t>lhr-14.mp3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -764,6 +1278,42 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Shop 6, Main Boulevard, DHA Phase 4, Lahore.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Shop 6, Main Boulevard, DHA Phase 4, Lahore.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -773,7 +1323,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>lhr-15.wav</t>
+          <t>lhr-15.mp3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -785,6 +1335,42 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>House 27, Street 5, Lake City, Lahore.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>House 27, Street 5, Lake City, Lahore.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -794,7 +1380,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>lhr-16.wav</t>
+          <t>lhr-16.mp3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -806,6 +1392,42 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Flat 15, Block D, Model Town Extension, Lahore.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Flat 15, Block D, Model Town Extension, Lahore.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -815,7 +1437,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>lhr-17.wav</t>
+          <t>lhr-17.mp3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -827,6 +1449,42 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Office 21, Emporium Mall, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Office 21, Emporium Mall, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -836,7 +1494,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>lhr-18.wav</t>
+          <t>lhr-18.mp3</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -848,6 +1506,42 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>House 63, Street 7, Township Lahore.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>House 63, Street 7, Township Lahore.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -857,7 +1551,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>lhr-19.wav</t>
+          <t>lhr-19.mp3</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -869,6 +1563,42 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Flat 4, Block A, Gulbeg 3, near Liberty Market, Lahore.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>S=2, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Flat 4, Block A, Gulberg III, near Liberty Market, Lahore.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -878,7 +1608,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>lhr-20.wav</t>
+          <t>lhr-20.mp3</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -890,6 +1620,168 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>House 36, Street 10, Wobdetown, near Canal Road, Lahore.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>S=1, D=1, I=0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>House 36, Street 10, Wapda Town, near Canal Road, Lahore.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>no keyterms</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>with keyterms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exact match</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average WER</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.014285</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-0.295005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Read this as</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Exact match should go up. WER should go down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Primary metric</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Normalized Exact Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Secondary diagnostic</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Word Error Rate (WER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Clips scored</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Region pack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pk-lahore (100 keyterms)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/measurement/lahore_recording_manifest.xlsx
+++ b/measurement/lahore_recording_manifest.xlsx
@@ -544,15 +544,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>S=1, D=1, I=0</t>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -562,15 +562,15 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S=1, D=1, I=0</t>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>0.35</v>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.30929</v>
+        <v>0.295005</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.014285</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>-0.295005</v>
